--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.79860618437509</v>
+        <v>6.792273504960952</v>
       </c>
       <c r="D2" t="n">
-        <v>42.45633241418961</v>
+        <v>6.899154017305812</v>
       </c>
       <c r="E2" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F2" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.25887401018536</v>
+        <v>5.729567026655121</v>
       </c>
       <c r="D3" t="n">
-        <v>35.8794408647881</v>
+        <v>5.830409140528067</v>
       </c>
       <c r="E3" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F3" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.19880231119114</v>
+        <v>5.23230537556856</v>
       </c>
       <c r="D4" t="n">
-        <v>31.60723391959281</v>
+        <v>5.136175511933831</v>
       </c>
       <c r="E4" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F4" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.557791487806911</v>
+        <v>1.228141116768623</v>
       </c>
       <c r="D5" t="n">
-        <v>8.060605667443156</v>
+        <v>1.309848420959513</v>
       </c>
       <c r="E5" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.62062653695676</v>
+        <v>5.625851812255473</v>
       </c>
       <c r="D6" t="n">
-        <v>34.52146542430645</v>
+        <v>5.609738131449798</v>
       </c>
       <c r="E6" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F6" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.68154926964051</v>
+        <v>3.685751756316583</v>
       </c>
       <c r="D7" t="n">
-        <v>23.14075627705867</v>
+        <v>3.760372895022034</v>
       </c>
       <c r="E7" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.2222787985908</v>
+        <v>6.373620304771006</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80492728123262</v>
+        <v>6.793300683200301</v>
       </c>
       <c r="E8" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F8" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.90084466047331</v>
+        <v>8.433887257326914</v>
       </c>
       <c r="D9" t="n">
-        <v>52.39227439331111</v>
+        <v>8.513744588913054</v>
       </c>
       <c r="E9" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F9" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.50544409133506</v>
+        <v>6.257134664841948</v>
       </c>
       <c r="D10" t="n">
-        <v>38.92422567624303</v>
+        <v>6.325186672389493</v>
       </c>
       <c r="E10" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F10" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.36076623686833</v>
+        <v>6.558624513491104</v>
       </c>
       <c r="D11" t="n">
-        <v>37.70319342424158</v>
+        <v>6.126768931439257</v>
       </c>
       <c r="E11" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F11" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.57916582835505</v>
+        <v>6.919114447107696</v>
       </c>
       <c r="D12" t="n">
-        <v>41.80130677432175</v>
+        <v>6.792712350827285</v>
       </c>
       <c r="E12" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F12" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.59178461006886</v>
+        <v>5.45866499913619</v>
       </c>
       <c r="D13" t="n">
-        <v>34.3356195471629</v>
+        <v>5.579538176413972</v>
       </c>
       <c r="E13" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F13" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.59659259529045</v>
+        <v>9.846946296734698</v>
       </c>
       <c r="D14" t="n">
-        <v>58.52468892152072</v>
+        <v>9.510261949747118</v>
       </c>
       <c r="E14" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F14" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>54.21717164051785</v>
+        <v>8.81029039158415</v>
       </c>
       <c r="D15" t="n">
-        <v>52.22320043360054</v>
+        <v>8.486270070460089</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F15" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.02747978348431</v>
+        <v>6.5044654648162</v>
       </c>
       <c r="D16" t="n">
-        <v>37.64430564754908</v>
+        <v>6.117199667726726</v>
       </c>
       <c r="E16" t="n">
-        <v>12.23471757065841</v>
+        <v>1.988141605231991</v>
       </c>
       <c r="F16" t="n">
-        <v>11.7432029358937</v>
+        <v>1.908270477082727</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
